--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484834_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484834_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6018</v>
+        <v>3.6665</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4124</v>
+        <v>3.5299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1894</v>
+        <v>0.1365</v>
       </c>
       <c r="G2" t="n">
         <v>1.4475</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2116</v>
+        <v>-0.147</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5139</v>
+        <v>-0.3963</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3022</v>
+        <v>0.2493</v>
       </c>
       <c r="V2" t="n">
         <v>1.4225</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0463</v>
+        <v>0.6644</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9607</v>
+        <v>5.1891</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9144</v>
+        <v>-4.5247</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.8393</v>
+        <v>3.3321</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8196</v>
+        <v>-0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0197</v>
+        <v>3.4589</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5566</v>
+        <v>6.8536</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2419</v>
+        <v>2.3775</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7985</v>
+        <v>4.4761</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3959</v>
+        <v>-3.5215</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5777</v>
+        <v>-2.5043</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8182</v>
+        <v>-1.0172</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2932</v>
+        <v>-0.5623</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1968</v>
+        <v>-0.7211</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0965</v>
+        <v>0.1588</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0827</v>
+        <v>-2.2941</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1245</v>
+        <v>-2.2941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1139</v>
+        <v>0.3948</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8766</v>
+        <v>2.2506</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.7627</v>
+        <v>-1.8558</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3321</v>
+        <v>1.3326</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1268</v>
+        <v>-0.6331</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4589</v>
+        <v>1.9657</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8536</v>
+        <v>3.9275</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3775</v>
+        <v>1.2044</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4761</v>
+        <v>2.7231</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5215</v>
+        <v>-2.5949</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5043</v>
+        <v>-1.8375</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0172</v>
+        <v>-0.7574</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1128</v>
+        <v>0.0356</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0335</v>
+        <v>0.2101</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0793</v>
+        <v>-0.1745</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2941</v>
+        <v>-1.3507</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2941</v>
+        <v>-1.3507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0765</v>
+        <v>0.0174</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8794</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8029</v>
+        <v>-0.7311</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3326</v>
+        <v>-0.077</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6331</v>
+        <v>-0.8303</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9657</v>
+        <v>0.7534</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9275</v>
+        <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2044</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7231</v>
+        <v>1.3162</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5949</v>
+        <v>-0.8069</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8375</v>
+        <v>-0.2442</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7574</v>
+        <v>-0.5628</v>
       </c>
       <c r="P5" t="n">
         <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2644</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2828</v>
+        <v>-0.283</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1611</v>
+        <v>0.0185</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1216</v>
+        <v>-0.3016</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3507</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2892</v>
+        <v>0.0043</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4948</v>
+        <v>2.1039</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.784</v>
+        <v>-2.0996</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.077</v>
+        <v>-2.8393</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8303</v>
+        <v>-1.8196</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7534</v>
+        <v>-1.0197</v>
       </c>
       <c r="J6" t="n">
-        <v>0.73</v>
+        <v>0.5566</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.2419</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3162</v>
+        <v>0.7985</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8069</v>
+        <v>-3.3959</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2442</v>
+        <v>-1.5777</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5628</v>
+        <v>-1.8182</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5896</v>
+        <v>0.2513</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2352</v>
+        <v>0.34</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3545</v>
+        <v>-0.0887</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0827</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1883</v>
+        <v>-1.2981</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6932</v>
+        <v>0.1238</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8814</v>
+        <v>-1.4219</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5949</v>
+        <v>-0.1505</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2594</v>
+        <v>0.7654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3356</v>
+        <v>-0.9159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5255</v>
+        <v>3.4357</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4375</v>
+        <v>2.6201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.963</v>
+        <v>0.8155</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1205</v>
+        <v>-3.5862</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8219</v>
+        <v>-1.8547</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2986</v>
+        <v>-1.7315</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5096</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5196</v>
+        <v>-0.242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4884</v>
+        <v>-0.4814</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0312</v>
+        <v>0.2393</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6226</v>
+        <v>0.038</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8537</v>
+        <v>-1.4604</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.617</v>
+        <v>0.421</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2367</v>
+        <v>-1.8814</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1505</v>
+        <v>-2.5949</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7654</v>
+        <v>-2.2594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9159</v>
+        <v>-0.3356</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4357</v>
+        <v>0.5255</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6201</v>
+        <v>-0.4375</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8155</v>
+        <v>0.963</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5862</v>
+        <v>-3.1205</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8547</v>
+        <v>-1.8219</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7315</v>
+        <v>-1.2986</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7977</v>
+        <v>0.2475</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2222</v>
+        <v>0.2163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4245</v>
+        <v>0.0312</v>
       </c>
       <c r="V8" t="n">
-        <v>0.038</v>
+        <v>-0.6226</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X8" t="n">
-        <v>0.038</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.739</v>
+        <v>-4.6597</v>
       </c>
       <c r="E9" t="n">
         <v>-3.9444</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7947</v>
+        <v>-0.7153</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9593</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3833</v>
+        <v>-0.3039</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3992</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0159</v>
+        <v>0.0953</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3208</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6363</v>
+        <v>-5.3154</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4567</v>
+        <v>-3.2417</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1796</v>
+        <v>-2.0738</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5016</v>
@@ -1234,13 +1234,13 @@
         <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1987</v>
+        <v>0.1221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4427</v>
+        <v>-0.2277</v>
       </c>
       <c r="U10" t="n">
-        <v>0.244</v>
+        <v>0.3498</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0489</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.868</v>
+        <v>-7.9862</v>
       </c>
       <c r="E11" t="n">
-        <v>6.299000000000001</v>
+        <v>7.1807</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.167</v>
+        <v>-15.1671</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0104</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.875599999999999</v>
+        <v>-4.8756</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8651999999999995</v>
+        <v>0.8652000000000004</v>
       </c>
       <c r="J11" t="n">
         <v>19.7177</v>
@@ -1303,7 +1303,7 @@
         <v>-8.7652</v>
       </c>
       <c r="P11" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q11" t="n">
         <v>-13.209</v>
@@ -1312,10 +1312,10 @@
         <v>13.209</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7637</v>
+        <v>-0.8817</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3226</v>
+        <v>-1.4408</v>
       </c>
       <c r="U11" t="n">
         <v>0.5589000000000001</v>
@@ -1327,7 +1327,7 @@
         <v>2.1126</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.2065</v>
+        <v>-5.206499999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.6994</v>
+        <v>6.4721</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8264</v>
+        <v>5.3393</v>
       </c>
       <c r="F12" t="n">
-        <v>0.873</v>
+        <v>1.1328</v>
       </c>
       <c r="G12" t="n">
         <v>5.2841</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5661</v>
+        <v>0.3388</v>
       </c>
       <c r="T12" t="n">
-        <v>0.77</v>
+        <v>0.2829</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2039</v>
+        <v>0.0559</v>
       </c>
       <c r="V12" t="n">
         <v>0.6606</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.512</v>
+        <v>2.8368</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8612</v>
+        <v>5.056</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3491</v>
+        <v>-2.2192</v>
       </c>
       <c r="G13" t="n">
         <v>2.2891</v>
@@ -1468,13 +1468,13 @@
         <v>2.0757</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0341</v>
+        <v>0.3589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3498</v>
+        <v>-0.155</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3839</v>
+        <v>0.5139</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9434</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8451</v>
+        <v>2.3068</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5369</v>
+        <v>2.3938</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6918</v>
+        <v>-0.0871</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2179</v>
+        <v>0.9119</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3038</v>
+        <v>1.3774</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9141</v>
+        <v>-0.4655</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7313</v>
+        <v>2.5915</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1158</v>
+        <v>2.4511</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6155</v>
+        <v>0.1404</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4865</v>
+        <v>-1.6796</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.188</v>
+        <v>-1.0737</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2986</v>
+        <v>-0.6059</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3839</v>
+        <v>0.3008</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4761</v>
+        <v>-0.1595</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0922</v>
+        <v>0.4603</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7356</v>
+        <v>1.8488</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7356</v>
+        <v>1.8488</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5045</v>
+        <v>1.827</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9067</v>
+        <v>2.4394</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4022</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9119</v>
+        <v>-3.2179</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3774</v>
+        <v>-1.3038</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4655</v>
+        <v>-1.9141</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5915</v>
+        <v>-0.7313</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4511</v>
+        <v>-0.1158</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1404</v>
+        <v>-0.6155</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6796</v>
+        <v>-2.4865</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0737</v>
+        <v>-1.188</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6059</v>
+        <v>-1.2986</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5014</v>
+        <v>0.3658</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.3787</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1452</v>
+        <v>-0.0129</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8488</v>
+        <v>3.7356</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8488</v>
+        <v>3.7356</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8304</v>
+        <v>0.747</v>
       </c>
       <c r="E16" t="n">
-        <v>2.043</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2126</v>
+        <v>-0.1808</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4755</v>
+        <v>2.944</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2138</v>
+        <v>2.8056</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7383</v>
+        <v>0.1384</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5669</v>
+        <v>5.5551</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2011</v>
+        <v>4.2049</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3658</v>
+        <v>1.3502</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0424</v>
+        <v>-2.6111</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4149</v>
+        <v>-1.3993</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-1.2118</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5096</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3433</v>
+        <v>0.0109</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4761</v>
+        <v>-0.5324</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8672</v>
+        <v>0.5432</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.547</v>
+        <v>0.6226</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0188</v>
+        <v>0.2763</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0063</v>
+        <v>1.396</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9875</v>
+        <v>-1.1197</v>
       </c>
       <c r="G17" t="n">
         <v>1.8359</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0512</v>
+        <v>0.3086</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7055</v>
+        <v>-0.3157</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.6243</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3021</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1503</v>
+        <v>0.1028</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3433</v>
+        <v>1.5558</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4936</v>
+        <v>-1.4531</v>
       </c>
       <c r="G18" t="n">
-        <v>2.944</v>
+        <v>-0.4755</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8056</v>
+        <v>-1.2138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1384</v>
+        <v>0.7383</v>
       </c>
       <c r="J18" t="n">
-        <v>5.5551</v>
+        <v>1.5669</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2049</v>
+        <v>0.2011</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3502</v>
+        <v>1.3658</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6111</v>
+        <v>-2.0424</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3993</v>
+        <v>-1.4149</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2118</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.8305</v>
+        <v>1.5096</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8864</v>
+        <v>0.6156</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.117</v>
+        <v>-0.0111</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2305</v>
+        <v>0.6267</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6226</v>
+        <v>-1.547</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1067</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9606</v>
+        <v>-1.058</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1461</v>
+        <v>0.246</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2873</v>
@@ -1936,13 +1936,13 @@
         <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0294</v>
+        <v>0.3241</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1147</v>
+        <v>-0.2121</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1441</v>
+        <v>0.5362</v>
       </c>
       <c r="V19" t="n">
         <v>0.019</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2852</v>
+        <v>-3.5896</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3961</v>
+        <v>-2.8833</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8891</v>
+        <v>-0.7063</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2741</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7436</v>
+        <v>0.4393</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6525</v>
+        <v>0.1653</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0912</v>
+        <v>0.274</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>8.868</v>
+        <v>10.1672</v>
       </c>
       <c r="E21" t="n">
-        <v>15.1671</v>
+        <v>15.1669</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.299</v>
+        <v>-4.9998</v>
       </c>
       <c r="G21" t="n">
         <v>4.0102</v>
@@ -2062,7 +2062,7 @@
         <v>4.8756</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8653000000000003</v>
+        <v>-0.8653000000000002</v>
       </c>
       <c r="J21" t="n">
         <v>23.7282</v>
@@ -2083,7 +2083,7 @@
         <v>-9.6303</v>
       </c>
       <c r="P21" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="Q21" t="n">
         <v>-13.209</v>
@@ -2092,13 +2092,13 @@
         <v>13.209</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7638</v>
+        <v>3.0628</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5589</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3226</v>
+        <v>3.6216</v>
       </c>
       <c r="V21" t="n">
         <v>3.0941</v>
